--- a/Team-Data/2012-13/3-10-2012-13.xlsx
+++ b/Team-Data/2012-13/3-10-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,19 +806,19 @@
         <v>0.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -787,7 +854,7 @@
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -843,34 +910,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
         <v>34</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.548</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>49.3</v>
       </c>
       <c r="I3" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L3" t="n">
         <v>5.9</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N3" t="n">
         <v>0.35</v>
@@ -882,19 +949,19 @@
         <v>20.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="R3" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S3" t="n">
         <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V3" t="n">
         <v>14.5</v>
@@ -915,13 +982,13 @@
         <v>19.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>12</v>
@@ -936,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ3" t="n">
         <v>26</v>
@@ -954,13 +1021,13 @@
         <v>22</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
         <v>23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
@@ -975,7 +1042,7 @@
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1136,7 +1203,7 @@
         <v>12</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
         <v>8</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-10.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,7 +1364,7 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1351,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" t="n">
         <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>0.556</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1407,40 +1474,40 @@
         <v>35.3</v>
       </c>
       <c r="J6" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L6" t="n">
         <v>4.9</v>
       </c>
       <c r="M6" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O6" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P6" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R6" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T6" t="n">
         <v>43.5</v>
       </c>
       <c r="U6" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V6" t="n">
         <v>14.7</v>
@@ -1455,19 +1522,19 @@
         <v>5.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
         <v>10</v>
@@ -1485,10 +1552,10 @@
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1503,16 +1570,16 @@
         <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
         <v>5</v>
       </c>
       <c r="AR6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -1536,13 +1603,13 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>28</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" t="n">
         <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1589,16 +1656,16 @@
         <v>36.5</v>
       </c>
       <c r="J7" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K7" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N7" t="n">
         <v>0.354</v>
@@ -1610,16 +1677,16 @@
         <v>23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.761</v>
+        <v>0.764</v>
       </c>
       <c r="R7" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S7" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="T7" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U7" t="n">
         <v>20.6</v>
@@ -1637,7 +1704,7 @@
         <v>7.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
         <v>20.2</v>
@@ -1649,16 +1716,16 @@
         <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG7" t="n">
         <v>26</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>27</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
@@ -1670,7 +1737,7 @@
         <v>4</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
@@ -1682,13 +1749,13 @@
         <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>8</v>
@@ -1697,7 +1764,7 @@
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU7" t="n">
         <v>26</v>
@@ -1715,7 +1782,7 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
         <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>0.468</v>
+        <v>0.459</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J8" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.457</v>
@@ -1786,31 +1853,31 @@
         <v>0.37</v>
       </c>
       <c r="O8" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="P8" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R8" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S8" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
         <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
         <v>5.4</v>
@@ -1819,7 +1886,7 @@
         <v>4.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA8" t="n">
         <v>19.4</v>
@@ -1828,19 +1895,19 @@
         <v>101.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1855,16 +1922,16 @@
         <v>10</v>
       </c>
       <c r="AL8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
         <v>21</v>
@@ -1876,10 +1943,10 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1897,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
         <v>22</v>
@@ -1906,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>4.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -2043,7 +2110,7 @@
         <v>18</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
@@ -2052,13 +2119,13 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AR9" t="n">
         <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
@@ -2067,7 +2134,7 @@
         <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2088,7 +2155,7 @@
         <v>3</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -2117,61 +2184,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>0.354</v>
+        <v>0.359</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J10" t="n">
-        <v>81.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L10" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="P10" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R10" t="n">
         <v>12.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
         <v>6.9</v>
@@ -2186,13 +2253,13 @@
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB10" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2201,49 +2268,49 @@
         <v>21</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>24</v>
       </c>
       <c r="AJ10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK10" t="n">
         <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR10" t="n">
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
@@ -2252,13 +2319,13 @@
         <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
@@ -2270,7 +2337,7 @@
         <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2398,7 +2465,7 @@
         <v>8</v>
       </c>
       <c r="AK11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
         <v>16</v>
@@ -2449,7 +2516,7 @@
         <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
@@ -2571,10 +2638,10 @@
         <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
         <v>10</v>
@@ -2592,7 +2659,7 @@
         <v>6</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
         <v>5</v>
@@ -2601,7 +2668,7 @@
         <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2610,7 +2677,7 @@
         <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2631,7 +2698,7 @@
         <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -2663,58 +2730,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" t="n">
         <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.619</v>
+        <v>0.629</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J13" t="n">
-        <v>80.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="K13" t="n">
         <v>0.435</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N13" t="n">
         <v>0.356</v>
       </c>
       <c r="O13" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.746</v>
+        <v>0.743</v>
       </c>
       <c r="R13" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S13" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T13" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
       <c r="U13" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V13" t="n">
         <v>15.2</v>
@@ -2732,16 +2799,16 @@
         <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2759,7 +2826,7 @@
         <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
         <v>25</v>
@@ -2768,13 +2835,13 @@
         <v>16</v>
       </c>
       <c r="AM13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
         <v>17</v>
       </c>
       <c r="AO13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -2783,7 +2850,7 @@
         <v>19</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2804,7 +2871,7 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2816,7 +2883,7 @@
         <v>25</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -2845,37 +2912,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="J14" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.36</v>
+        <v>0.357</v>
       </c>
       <c r="O14" t="n">
         <v>16.5</v>
@@ -2884,43 +2951,43 @@
         <v>23.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.706</v>
+        <v>0.707</v>
       </c>
       <c r="R14" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S14" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T14" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
         <v>14.9</v>
       </c>
       <c r="W14" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y14" t="n">
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA14" t="n">
         <v>21</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.1</v>
+        <v>100.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2932,13 +2999,13 @@
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
         <v>24</v>
@@ -2947,13 +3014,13 @@
         <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
         <v>10</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>19</v>
@@ -2965,13 +3032,13 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>21</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -2989,7 +3056,7 @@
         <v>6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15" t="n">
         <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>0.516</v>
+        <v>0.508</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
@@ -3045,7 +3112,7 @@
         <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K15" t="n">
         <v>0.46</v>
@@ -3057,28 +3124,28 @@
         <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.358</v>
+        <v>0.361</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="S15" t="n">
         <v>33</v>
       </c>
       <c r="T15" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U15" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
@@ -3087,7 +3154,7 @@
         <v>7.1</v>
       </c>
       <c r="X15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y15" t="n">
         <v>5.1</v>
@@ -3096,16 +3163,16 @@
         <v>18.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.5</v>
+        <v>102.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>15</v>
@@ -3135,19 +3202,19 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
         <v>3</v>
@@ -3168,7 +3235,7 @@
         <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>4</v>
@@ -3180,7 +3247,7 @@
         <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3296,19 +3363,19 @@
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
@@ -3338,10 +3405,10 @@
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.77</v>
+        <v>0.767</v>
       </c>
       <c r="H17" t="n">
         <v>48.7</v>
@@ -3409,37 +3476,37 @@
         <v>39</v>
       </c>
       <c r="J17" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.496</v>
+        <v>0.495</v>
       </c>
       <c r="L17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.388</v>
+        <v>0.387</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R17" t="n">
         <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T17" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="U17" t="n">
         <v>22.5</v>
@@ -3454,10 +3521,10 @@
         <v>5.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AA17" t="n">
         <v>20.4</v>
@@ -3466,10 +3533,10 @@
         <v>103.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3493,22 +3560,22 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN17" t="n">
         <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
         <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>28</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -3573,22 +3640,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" t="n">
         <v>29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.525</v>
+        <v>0.517</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J18" t="n">
         <v>86.8</v>
@@ -3606,19 +3673,19 @@
         <v>0.356</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="P18" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q18" t="n">
         <v>0.736</v>
       </c>
       <c r="R18" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S18" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T18" t="n">
         <v>43.6</v>
@@ -3627,7 +3694,7 @@
         <v>22.8</v>
       </c>
       <c r="V18" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W18" t="n">
         <v>8.5</v>
@@ -3639,22 +3706,22 @@
         <v>4.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
         <v>13</v>
@@ -3675,7 +3742,7 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM18" t="n">
         <v>19</v>
@@ -3684,10 +3751,10 @@
         <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
         <v>22</v>
@@ -3717,10 +3784,10 @@
         <v>8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
         <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>0.35</v>
+        <v>0.356</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,43 +3840,43 @@
         <v>35.3</v>
       </c>
       <c r="J19" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.431</v>
+        <v>0.433</v>
       </c>
       <c r="L19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M19" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.293</v>
+        <v>0.296</v>
       </c>
       <c r="O19" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P19" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="R19" t="n">
         <v>12.6</v>
       </c>
       <c r="S19" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T19" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U19" t="n">
         <v>21.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W19" t="n">
         <v>8.300000000000001</v>
@@ -3824,19 +3891,19 @@
         <v>18.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3.5</v>
+        <v>-3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF19" t="n">
         <v>20</v>
@@ -3878,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="AS19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -3887,7 +3954,7 @@
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>11</v>
@@ -3896,7 +3963,7 @@
         <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ19" t="n">
         <v>5</v>
@@ -3905,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F20" t="n">
         <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0.344</v>
+        <v>0.333</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,46 +4022,46 @@
         <v>36.3</v>
       </c>
       <c r="J20" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K20" t="n">
         <v>0.451</v>
       </c>
       <c r="L20" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M20" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.372</v>
+        <v>0.369</v>
       </c>
       <c r="O20" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P20" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="Q20" t="n">
         <v>0.772</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S20" t="n">
         <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
         <v>14.3</v>
       </c>
       <c r="W20" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X20" t="n">
         <v>5.6</v>
@@ -4003,49 +4070,49 @@
         <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
         <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>25</v>
@@ -4057,16 +4124,16 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
@@ -4078,19 +4145,19 @@
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4212,13 +4279,13 @@
         <v>29</v>
       </c>
       <c r="AI21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ21" t="n">
         <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>2</v>
@@ -4227,13 +4294,13 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
         <v>18</v>
       </c>
       <c r="AP21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ21" t="n">
         <v>14</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -4301,49 +4368,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
         <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.746</v>
+        <v>0.742</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J22" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="L22" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M22" t="n">
         <v>19.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.39</v>
+        <v>0.392</v>
       </c>
       <c r="O22" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.831</v>
+        <v>0.832</v>
       </c>
       <c r="R22" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S22" t="n">
         <v>32.8</v>
@@ -4361,25 +4428,25 @@
         <v>8.4</v>
       </c>
       <c r="X22" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z22" t="n">
         <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.7</v>
+        <v>107</v>
       </c>
       <c r="AC22" t="n">
         <v>9.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,7 +4461,7 @@
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
         <v>28</v>
@@ -4406,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="AM22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN22" t="n">
         <v>2</v>
@@ -4424,10 +4491,10 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
         <v>18</v>
@@ -4445,13 +4512,13 @@
         <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
         <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23" t="n">
         <v>46</v>
       </c>
       <c r="G23" t="n">
-        <v>0.281</v>
+        <v>0.27</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4504,40 +4571,40 @@
         <v>83.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L23" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.335</v>
+        <v>0.333</v>
       </c>
       <c r="O23" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="Q23" t="n">
         <v>0.772</v>
       </c>
       <c r="R23" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
         <v>42.3</v>
       </c>
       <c r="U23" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
         <v>6.1</v>
@@ -4549,19 +4616,19 @@
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4582,7 +4649,7 @@
         <v>9</v>
       </c>
       <c r="AK23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4606,13 +4673,13 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" t="n">
-        <v>0.371</v>
+        <v>0.377</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4695,19 +4762,19 @@
         <v>17.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="P24" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="R24" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S24" t="n">
         <v>30.7</v>
@@ -4719,19 +4786,19 @@
         <v>22.4</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W24" t="n">
         <v>7.3</v>
       </c>
       <c r="X24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y24" t="n">
         <v>4.8</v>
       </c>
-      <c r="Y24" t="n">
-        <v>4.9</v>
-      </c>
       <c r="Z24" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA24" t="n">
         <v>16.3</v>
@@ -4743,7 +4810,7 @@
         <v>-4</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>21</v>
@@ -4758,22 +4825,22 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,13 +4852,13 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
         <v>14</v>
@@ -4803,13 +4870,13 @@
         <v>21</v>
       </c>
       <c r="AX24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>23</v>
@@ -4937,13 +5004,13 @@
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
         <v>13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK25" t="n">
         <v>21</v>
@@ -4967,13 +5034,13 @@
         <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS25" t="n">
         <v>23</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
         <v>15</v>
@@ -4997,7 +5064,7 @@
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" t="n">
         <v>29</v>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G26" t="n">
-        <v>0.468</v>
+        <v>0.475</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
@@ -5047,37 +5114,37 @@
         <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M26" t="n">
         <v>23.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O26" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P26" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R26" t="n">
         <v>11.1</v>
       </c>
       <c r="S26" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U26" t="n">
         <v>21.6</v>
@@ -5089,16 +5156,16 @@
         <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
         <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB26" t="n">
         <v>98</v>
@@ -5107,7 +5174,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,25 +5186,25 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI26" t="n">
         <v>18</v>
       </c>
       <c r="AJ26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK26" t="n">
         <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM26" t="n">
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO26" t="n">
         <v>20</v>
@@ -5152,10 +5219,10 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
@@ -5164,16 +5231,16 @@
         <v>15</v>
       </c>
       <c r="AW26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>23</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" t="n">
         <v>22</v>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G27" t="n">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J27" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.443</v>
@@ -5241,13 +5308,13 @@
         <v>19.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O27" t="n">
         <v>17.7</v>
       </c>
       <c r="P27" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="n">
         <v>0.767</v>
@@ -5262,28 +5329,28 @@
         <v>40.5</v>
       </c>
       <c r="U27" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V27" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W27" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y27" t="n">
         <v>6.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC27" t="n">
         <v>-6.1</v>
@@ -5295,22 +5362,22 @@
         <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ27" t="n">
         <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>14</v>
@@ -5325,7 +5392,7 @@
         <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
         <v>12</v>
@@ -5343,7 +5410,7 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW27" t="n">
         <v>9</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,10 +5571,10 @@
         <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -5575,19 +5642,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.391</v>
+        <v>0.381</v>
       </c>
       <c r="H29" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I29" t="n">
         <v>36.4</v>
@@ -5596,7 +5663,7 @@
         <v>82.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L29" t="n">
         <v>7.4</v>
@@ -5608,10 +5675,10 @@
         <v>0.351</v>
       </c>
       <c r="O29" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P29" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q29" t="n">
         <v>0.782</v>
@@ -5620,10 +5687,10 @@
         <v>10.8</v>
       </c>
       <c r="S29" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U29" t="n">
         <v>22</v>
@@ -5632,34 +5699,34 @@
         <v>13.3</v>
       </c>
       <c r="W29" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X29" t="n">
         <v>4.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z29" t="n">
         <v>22.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB29" t="n">
         <v>97.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
         <v>20</v>
@@ -5668,31 +5735,31 @@
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL29" t="n">
         <v>11</v>
       </c>
-      <c r="AK29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>12</v>
-      </c>
       <c r="AM29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN29" t="n">
         <v>21</v>
       </c>
       <c r="AO29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
         <v>22</v>
@@ -5713,22 +5780,22 @@
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB29" t="n">
         <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -5835,25 +5902,25 @@
         <v>-0.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF30" t="n">
         <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>8</v>
       </c>
       <c r="AI30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>14</v>
@@ -5886,10 +5953,10 @@
         <v>14</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6047,7 +6114,7 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
@@ -6062,7 +6129,7 @@
         <v>23</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT31" t="n">
         <v>7</v>
@@ -6092,7 +6159,7 @@
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-10-2012-13</t>
+          <t>2013-03-10</t>
         </is>
       </c>
     </row>
